--- a/xiuxian配置表/indir/修炼方法.xlsx
+++ b/xiuxian配置表/indir/修炼方法.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="885" yWindow="3795" windowWidth="27330" windowHeight="11025" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_xiulian_methods" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_xiulian_methods_effectCatalog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_xiulian_methods_families" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_xiulian_methods_metadata" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_xiulian_methods_methods" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="z_xiulian_methods" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="z_xiulian_methods_effectCatalog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="z_xiulian_methods_families" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="z_xiulian_methods_metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="z_xiulian_methods_methods" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4652,7 +4652,7 @@
     <row r="151" ht="27" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>tribulation_control</t>
+          <t>dujie_control</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="152" ht="27" customHeight="1">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>tribulation_damage</t>
+          <t>dujie_damage</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -4706,7 +4706,7 @@
     <row r="153" ht="27" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>tribulation_energy_absorption</t>
+          <t>dujie_energy_absorption</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -4733,7 +4733,7 @@
     <row r="154" ht="27" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>tribulation_forecast</t>
+          <t>dujie_forecast</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -4760,7 +4760,7 @@
     <row r="155" ht="27" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>tribulation_plan_slots</t>
+          <t>dujie_plan_slots</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -4787,7 +4787,7 @@
     <row r="156" ht="27" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>tribulation_recovery</t>
+          <t>dujie_recovery</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -4814,7 +4814,7 @@
     <row r="157" ht="27" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>tribulation_resistance</t>
+          <t>dujie_resistance</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="158" ht="27" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>tribulation_resource_efficiency</t>
+          <t>dujie_resource_efficiency</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -4868,7 +4868,7 @@
     <row r="159" ht="27" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>tribulation_sever</t>
+          <t>dujie_sever</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -4895,7 +4895,7 @@
     <row r="160" ht="27" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>tribulation_warning_time</t>
+          <t>dujie_warning_time</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -4976,7 +4976,7 @@
     <row r="163" ht="27" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>void_herb_growth</t>
+          <t>lianxu_herb_growth</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5003,7 +5003,7 @@
     <row r="164" ht="27" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>void_mobility</t>
+          <t>lianxu_mobility</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -5030,7 +5030,7 @@
     <row r="165" ht="27" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>void_resistance</t>
+          <t>lianxu_resistance</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="166" ht="27" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>void_route_safety</t>
+          <t>lianxu_route_safety</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5084,7 +5084,7 @@
     <row r="167" ht="27" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>void_ship_range</t>
+          <t>lianxu_ship_range</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="168" ht="27" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>void_spell_accuracy</t>
+          <t>lianxu_spell_accuracy</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -5138,7 +5138,7 @@
     <row r="169" ht="27" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>void_survival</t>
+          <t>lianxu_survival</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="170" ht="27" customHeight="1">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>void_target_accuracy</t>
+          <t>lianxu_target_accuracy</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N5" s="3" t="n"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_resistance", "base": 0.24, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.03}, {"effectId": "immortal_qi_conversion", "base": 0.22, "operation": "add_percent", "stackGroup": "immortal_qi_conversion", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "cultivation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.03}, {"effectId": "ascension_stability", "base": 0.24, "operation": "add_percent", "stackGroup": "ascension_stability", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.07}]</t>
+          <t>[{"effectId":"tribulation_resistance","base":0.24,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.03},{"effectId":"immortal_qi_conversion","base":0.22,"operation":"add_percent","stackGroup":"immortal_qi_conversion","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"cultivation","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.03},{"effectId":"ascension_stability","base":0.24,"operation":"add_percent","stackGroup":"ascension_stability","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.07}]</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N14" s="3" t="n"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F25" s="8" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N32" s="3" t="n"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F35" s="8" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F37" s="8" t="n">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F39" s="8" t="n">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_resistance", "base": 0.4, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.045}, {"effectId": "all_resistance", "base": 0.28, "operation": "add_percent", "stackGroup": "all_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.035}, {"effectId": "tribulation_energy_absorption", "base": 0.3, "operation": "add_percent", "stackGroup": "tribulation_energy_absorption", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.09}]</t>
+          <t>[{"effectId":"tribulation_resistance","base":0.4,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.045},{"effectId":"all_resistance","base":0.28,"operation":"add_percent","stackGroup":"all_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.035},{"effectId":"tribulation_energy_absorption","base":0.3,"operation":"add_percent","stackGroup":"tribulation_energy_absorption","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.09}]</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F47" s="8" t="n">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "mental_resistance", "base": 0.396, "operation": "add_percent", "stackGroup": "mental_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "causality_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "causality_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "causality_detection", "base": 0.264, "operation": "add_percent", "stackGroup": "causality_detection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.077}]</t>
+          <t>[{"effectId":"mental_resistance","base":0.396,"operation":"add_percent","stackGroup":"mental_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"causality_resistance","base":0.22,"operation":"add_percent","stackGroup":"causality_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.033},{"effectId":"causality_detection","base":0.264,"operation":"add_percent","stackGroup":"causality_detection","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.077}]</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F49" s="8" t="n">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "heart_tribulation_resistance", "base": 0.55, "operation": "add_percent", "stackGroup": "heart_tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "tribulation_control", "base": 0.242, "operation": "add_percent", "stackGroup": "tribulation_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "heart_tribulation_insight", "base": 0.352, "operation": "add_percent", "stackGroup": "heart_tribulation_insight", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.099}]</t>
+          <t>[{"effectId":"heart_tribulation_resistance","base":0.55,"operation":"add_percent","stackGroup":"heart_tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.055},{"effectId":"tribulation_control","base":0.242,"operation":"add_percent","stackGroup":"tribulation_control","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"control","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"heart_tribulation_insight","base":0.352,"operation":"add_percent","stackGroup":"heart_tribulation_insight","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.099}]</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N50" s="3" t="n"/>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F53" s="8" t="n">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F55" s="8" t="n">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "law_spell_power", "base": 0.352, "operation": "add_percent", "stackGroup": "law_spell_power", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "thunder_damage", "base": 0.638, "operation": "add_percent", "stackGroup": "thunder_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.055}, {"effectId": "law_spell_efficiency", "base": 0.275, "operation": "add_percent", "stackGroup": "law_spell_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.077}]</t>
+          <t>[{"effectId":"law_spell_power","base":0.352,"operation":"add_percent","stackGroup":"law_spell_power","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"thunder_damage","base":0.638,"operation":"add_percent","stackGroup":"thunder_damage","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"offense","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.055},{"effectId":"law_spell_efficiency","base":0.275,"operation":"add_percent","stackGroup":"law_spell_efficiency","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.077}]</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_damage", "base": 0.605, "operation": "add_percent", "stackGroup": "tribulation_damage", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "offense", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.061}, {"effectId": "tribulation_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.033}, {"effectId": "tribulation_energy_absorption", "base": 0.33, "operation": "add_percent", "stackGroup": "tribulation_energy_absorption", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.099}]</t>
+          <t>[{"effectId":"tribulation_damage","base":0.605,"operation":"add_percent","stackGroup":"tribulation_damage","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"offense","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.061},{"effectId":"tribulation_resistance","base":0.22,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.033},{"effectId":"tribulation_energy_absorption","base":0.33,"operation":"add_percent","stackGroup":"tribulation_energy_absorption","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.099}]</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N59" s="3" t="n"/>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F63" s="8" t="n">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F65" s="8" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F67" s="8" t="n">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "qi", "knowledge": []}</t>
+          <t>{"realm": "lianqi", "knowledge": []}</t>
         </is>
       </c>
       <c r="N68" s="3" t="n"/>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F69" s="8" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>nascent</t>
+          <t>yuanying</t>
         </is>
       </c>
       <c r="F71" s="8" t="n">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "nascent", "knowledge": []}</t>
+          <t>{"realm": "yuanying", "knowledge": []}</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F73" s="8" t="n">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F75" s="8" t="n">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>huashen</t>
         </is>
       </c>
       <c r="F77" s="8" t="n">
@@ -12329,12 +12329,12 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_forecast", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_forecast", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "karma_resistance", "base": 0.132, "operation": "add_percent", "stackGroup": "karma_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.024}, {"effectId": "tribulation_warning_time", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_warning_time", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "exploration", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.055}]</t>
+          <t>[{"effectId":"tribulation_forecast","base":0.198,"operation":"add_percent","stackGroup":"tribulation_forecast","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.033},{"effectId":"karma_resistance","base":0.132,"operation":"add_percent","stackGroup":"karma_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.024},{"effectId":"tribulation_warning_time","base":0.198,"operation":"add_percent","stackGroup":"tribulation_warning_time","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"exploration","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.055}]</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "transform", "knowledge": []}</t>
+          <t>{"realm": "huashen", "knowledge": []}</t>
         </is>
       </c>
       <c r="N77" s="3" t="n"/>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "law_resistance", "base": 0.22, "operation": "add_percent", "stackGroup": "law_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.033}, {"effectId": "tribulation_forecast", "base": 0.308, "operation": "add_percent", "stackGroup": "tribulation_forecast", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "law_seed_growth", "base": 0.242, "operation": "add_percent", "stackGroup": "law_seed_growth", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
+          <t>[{"effectId":"law_resistance","base":0.22,"operation":"add_percent","stackGroup":"law_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.033},{"effectId":"tribulation_forecast","base":0.308,"operation":"add_percent","stackGroup":"tribulation_forecast","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"law_seed_growth","base":0.242,"operation":"add_percent","stackGroup":"law_seed_growth","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.066}]</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "void", "knowledge": []}</t>
+          <t>{"realm": "lianxu", "knowledge": []}</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
       <c r="F79" s="8" t="n">
@@ -12491,12 +12491,12 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "law_resistance", "base": 0.374, "operation": "add_percent", "stackGroup": "law_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "tribulation_control", "base": 0.198, "operation": "add_percent", "stackGroup": "tribulation_control", "stackPolicy": "highest", "activation": "active_method", "cap": 2, "attributes": {"category": "control", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.031}, {"effectId": "tribulation_plan_slots", "base": 1.1, "operation": "add_flat", "stackGroup": "tribulation_plan_slots", "stackPolicy": "highest", "activation": "active_method", "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "flat", "displayPriority": 3}, "masteryGrowth": 1.1}]</t>
+          <t>[{"effectId":"law_resistance","base":0.374,"operation":"add_percent","stackGroup":"law_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"tribulation_control","base":0.198,"operation":"add_percent","stackGroup":"tribulation_control","stackPolicy":"highest","activation":"active_method","cap":2,"attributes":{"category":"control","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.031},{"effectId":"tribulation_plan_slots","base":1.1,"operation":"add_flat","stackGroup":"tribulation_plan_slots","stackPolicy":"highest","activation":"active_method","attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"flat","displayPriority":3},"masteryGrowth":1.1}]</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "merge", "knowledge": []}</t>
+          <t>{"realm": "heti", "knowledge": []}</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>dacheng</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
@@ -12574,12 +12574,12 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_resistance", "base": 0.352, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.044}, {"effectId": "heart_tribulation_resistance", "base": 0.33, "operation": "add_percent", "stackGroup": "heart_tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.044}, {"effectId": "tribulation_resource_efficiency", "base": 0.308, "operation": "add_percent", "stackGroup": "tribulation_resource_efficiency", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.088}]</t>
+          <t>[{"effectId":"tribulation_resistance","base":0.352,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.044},{"effectId":"heart_tribulation_resistance","base":0.33,"operation":"add_percent","stackGroup":"heart_tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.044},{"effectId":"tribulation_resource_efficiency","base":0.308,"operation":"add_percent","stackGroup":"tribulation_resource_efficiency","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.088}]</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "great", "knowledge": []}</t>
+          <t>{"realm": "dacheng", "knowledge": []}</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
       <c r="F81" s="8" t="n">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>[{"effectId": "tribulation_resistance", "base": 0.55, "operation": "add_percent", "stackGroup": "tribulation_resistance", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.85, "attributes": {"category": "survival", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 1}, "masteryGrowth": 0.055}, {"effectId": "ascension_success", "base": 0.264, "operation": "add_percent", "stackGroup": "ascension_success", "stackPolicy": "add_capped", "activation": "active_method", "cap": 0.75, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 2}, "masteryGrowth": 0.039}, {"effectId": "ascension_failure_protection", "base": 0.22, "operation": "add_percent", "stackGroup": "ascension_failure_protection", "stackPolicy": "add_capped", "activation": "active_method", "cap": 2, "attributes": {"category": "tribulation", "target": "self", "polarity": "positive", "valueType": "ratio", "displayPriority": 3}, "masteryGrowth": 0.066}]</t>
+          <t>[{"effectId":"tribulation_resistance","base":0.55,"operation":"add_percent","stackGroup":"tribulation_resistance","stackPolicy":"add_capped","activation":"active_method","cap":0.85,"attributes":{"category":"survival","target":"self","polarity":"positive","valueType":"ratio","displayPriority":1},"masteryGrowth":0.055},{"effectId":"ascension_success","base":0.264,"operation":"add_percent","stackGroup":"ascension_success","stackPolicy":"add_capped","activation":"active_method","cap":0.75,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":2},"masteryGrowth":0.039},{"effectId":"ascension_failure_protection","base":0.22,"operation":"add_percent","stackGroup":"ascension_failure_protection","stackPolicy":"add_capped","activation":"active_method","cap":2,"attributes":{"category":"dujie","target":"self","polarity":"positive","valueType":"ratio","displayPriority":3},"masteryGrowth":0.066}]</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "tribulation", "knowledge": []}</t>
+          <t>{"realm": "dujie", "knowledge": []}</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N82" s="3" t="n"/>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F83" s="8" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N83" s="3" t="n"/>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N84" s="3" t="n"/>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F85" s="8" t="n">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N85" s="3" t="n"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
       <c r="F86" s="8" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "core", "knowledge": []}</t>
+          <t>{"realm": "jindan", "knowledge": []}</t>
         </is>
       </c>
       <c r="N86" s="3" t="n"/>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
       <c r="F87" s="8" t="n">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>{"realm": "foundation", "knowledge": []}</t>
+          <t>{"realm": "zhuji", "knowledge": []}</t>
         </is>
       </c>
       <c r="N87" s="3" t="n"/>
